--- a/api/src/excelreports/reportTemplates/Routers.xlsx
+++ b/api/src/excelreports/reportTemplates/Routers.xlsx
@@ -142,9 +142,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Reporting For</t>
-  </si>
-  <si>
     <t>Last Seen</t>
   </si>
   <si>
@@ -155,6 +152,9 @@
   </si>
   <si>
     <t>&lt;lastSeen&gt;</t>
+  </si>
+  <si>
+    <t>Reporting Since</t>
   </si>
 </sst>
 </file>
@@ -808,10 +808,10 @@
         <v>39</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -819,13 +819,13 @@
         <v>33</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
